--- a/main/ig/CdaToCodeConceptMap.xlsx
+++ b/main/ig/CdaToCodeConceptMap.xlsx
@@ -65,7 +65,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-13T12:18:34+00:00</t>
+    <t>2026-04-14T12:56:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CdaToCodeConceptMap.xlsx
+++ b/main/ig/CdaToCodeConceptMap.xlsx
@@ -65,7 +65,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-14T12:56:47+00:00</t>
+    <t>2026-04-14T13:00:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/CdaToCodeConceptMap.xlsx
+++ b/main/ig/CdaToCodeConceptMap.xlsx
@@ -65,7 +65,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-14T13:00:40+00:00</t>
+    <t>2026-04-14T13:24:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
